--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -1589,7 +1589,7 @@
         <v>88</v>
       </c>
       <c r="E53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F53" s="1">
         <v>3</v>
@@ -1612,7 +1612,7 @@
         <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F54" s="1">
         <v>3</v>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="477" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="527" uniqueCount="107">
   <si>
     <t>pull_item</t>
   </si>
@@ -21,15 +21,15 @@
     <t>liquor (e.g, whisky, coconut wine)</t>
   </si>
   <si>
+    <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+  </si>
+  <si>
     <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
   </si>
   <si>
     <t>camote</t>
   </si>
   <si>
-    <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
-  </si>
-  <si>
     <t>chicken</t>
   </si>
   <si>
@@ -162,9 +162,6 @@
     <t>ALIMODIAN</t>
   </si>
   <si>
-    <t>ANILAO</t>
-  </si>
-  <si>
     <t>BALASAN</t>
   </si>
   <si>
@@ -174,6 +171,9 @@
     <t>BAROTAC NUEVO</t>
   </si>
   <si>
+    <t>BAROTAC VIEJO</t>
+  </si>
+  <si>
     <t>BATAD</t>
   </si>
   <si>
@@ -273,15 +273,15 @@
     <t>lipid/lapad</t>
   </si>
   <si>
+    <t>putos</t>
+  </si>
+  <si>
     <t>small cup</t>
   </si>
   <si>
     <t>binilog</t>
   </si>
   <si>
-    <t>putos</t>
-  </si>
-  <si>
     <t>bilog</t>
   </si>
   <si>
@@ -294,6 +294,9 @@
     <t>medium packs</t>
   </si>
   <si>
+    <t>papaya, mango, banana</t>
+  </si>
+  <si>
     <t>refilled</t>
   </si>
   <si>
@@ -303,10 +306,10 @@
     <t>tumpok</t>
   </si>
   <si>
+    <t>pack</t>
+  </si>
+  <si>
     <t>pieces</t>
-  </si>
-  <si>
-    <t>pack</t>
   </si>
   <si>
     <t>cone</t>
@@ -376,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -393,13 +396,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
@@ -416,7 +419,7 @@
         <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -439,7 +442,7 @@
         <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -462,7 +465,7 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -479,13 +482,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -502,13 +505,13 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -519,19 +522,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -548,13 +551,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
         <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -565,7 +568,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -574,7 +577,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>103</v>
@@ -588,19 +591,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -611,30 +614,30 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>103</v>
       </c>
       <c r="F11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -643,33 +646,33 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -686,13 +689,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -703,16 +706,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>103</v>
@@ -726,19 +729,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -749,19 +752,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -772,16 +775,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
         <v>103</v>
@@ -795,7 +798,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -804,10 +807,10 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -818,30 +821,30 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -850,7 +853,7 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
         <v>103</v>
@@ -864,19 +867,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -887,16 +890,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
         <v>103</v>
@@ -910,19 +913,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -933,7 +936,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -942,33 +945,33 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F26" s="1">
         <v>2</v>
@@ -979,16 +982,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
         <v>103</v>
@@ -1002,65 +1005,65 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F28" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1077,36 +1080,36 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
         <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F32" s="1">
         <v>3</v>
@@ -1117,42 +1120,42 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F33" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F34" s="1">
         <v>3</v>
@@ -1163,42 +1166,42 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
         <v>103</v>
       </c>
       <c r="F35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -1209,39 +1212,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E37" t="s">
         <v>103</v>
       </c>
       <c r="F37" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
         <v>103</v>
@@ -1255,7 +1258,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -1267,7 +1270,7 @@
         <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1278,7 +1281,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
         <v>18</v>
@@ -1287,10 +1290,10 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F40" s="1">
         <v>3</v>
@@ -1301,65 +1304,65 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F41" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F42" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F43" s="1">
         <v>3</v>
@@ -1370,19 +1373,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -1393,108 +1396,108 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F45" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B46" t="s">
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F46" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F47" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F48" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E49" t="s">
         <v>103</v>
@@ -1508,19 +1511,19 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F50" s="1">
         <v>3</v>
@@ -1531,25 +1534,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1560,13 +1563,13 @@
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
         <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F52" s="1">
         <v>2</v>
@@ -1577,19 +1580,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F53" s="1">
         <v>3</v>
@@ -1606,42 +1609,42 @@
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D55" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F55" s="1">
         <v>3</v>
       </c>
       <c r="G55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1652,19 +1655,19 @@
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F56" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1675,13 +1678,13 @@
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D57" t="s">
         <v>85</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F57" s="1">
         <v>2</v>
@@ -1692,209 +1695,209 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
         <v>103</v>
       </c>
       <c r="F58" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D59" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F60" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E61" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E62" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F62" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E63" t="s">
         <v>103</v>
       </c>
       <c r="F63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D64" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
       </c>
       <c r="G64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E65" t="s">
         <v>103</v>
       </c>
       <c r="F65" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F66" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1905,13 +1908,13 @@
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
         <v>85</v>
       </c>
       <c r="E67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F67" s="1">
         <v>2</v>
@@ -1928,19 +1931,19 @@
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
         <v>84</v>
       </c>
       <c r="E68" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F68" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -1951,174 +1954,174 @@
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E69" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F69" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D70" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B71" t="s">
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D72" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F72" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D73" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E73" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F73" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D74" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E74" t="s">
         <v>103</v>
       </c>
       <c r="F74" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D75" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E75" t="s">
         <v>103</v>
       </c>
       <c r="F75" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D76" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F76" s="1">
         <v>3</v>
@@ -2135,13 +2138,13 @@
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E77" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
@@ -2152,25 +2155,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B78" t="s">
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E78" t="s">
         <v>103</v>
       </c>
       <c r="F78" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2181,13 +2184,13 @@
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D79" t="s">
         <v>84</v>
       </c>
       <c r="E79" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F79" s="1">
         <v>2</v>
@@ -2198,25 +2201,25 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D80" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F80" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2227,13 +2230,13 @@
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D81" t="s">
         <v>85</v>
       </c>
       <c r="E81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -2244,16 +2247,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E82" t="s">
         <v>103</v>
@@ -2273,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F83" s="1">
         <v>3</v>
@@ -2290,65 +2293,65 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D84" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E84" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G84" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F85" s="1">
         <v>3</v>
       </c>
       <c r="G85" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D86" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E86" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F86" s="1">
         <v>2</v>
@@ -2359,62 +2362,62 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E87" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F87" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D88" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E88" t="s">
         <v>103</v>
       </c>
       <c r="F88" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G88" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D89" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E89" t="s">
         <v>103</v>
@@ -2428,42 +2431,42 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E90" t="s">
         <v>103</v>
       </c>
       <c r="F90" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F91" s="1">
         <v>3</v>
@@ -2474,19 +2477,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C92" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D92" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E92" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F92" s="1">
         <v>3</v>
@@ -2497,19 +2500,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D93" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E93" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F93" s="1">
         <v>3</v>
@@ -2520,47 +2523,277 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D94" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E94" t="s">
         <v>103</v>
       </c>
       <c r="F94" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>75</v>
+      </c>
+      <c r="D95" t="s">
+        <v>91</v>
+      </c>
+      <c r="E95" t="s">
+        <v>104</v>
+      </c>
+      <c r="F95" s="1">
+        <v>3</v>
+      </c>
+      <c r="G95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" t="s">
+        <v>76</v>
+      </c>
+      <c r="D96" t="s">
+        <v>98</v>
+      </c>
+      <c r="E96" t="s">
+        <v>103</v>
+      </c>
+      <c r="F96" s="1">
+        <v>2</v>
+      </c>
+      <c r="G96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" t="s">
+        <v>77</v>
+      </c>
+      <c r="D97" t="s">
+        <v>86</v>
+      </c>
+      <c r="E97" t="s">
+        <v>104</v>
+      </c>
+      <c r="F97" s="1">
+        <v>2</v>
+      </c>
+      <c r="G97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
         <v>19</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C98" t="s">
+        <v>78</v>
+      </c>
+      <c r="D98" t="s">
+        <v>101</v>
+      </c>
+      <c r="E98" t="s">
+        <v>104</v>
+      </c>
+      <c r="F98" s="1">
+        <v>3</v>
+      </c>
+      <c r="G98" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" t="s">
+        <v>78</v>
+      </c>
+      <c r="D99" t="s">
+        <v>100</v>
+      </c>
+      <c r="E99" t="s">
+        <v>104</v>
+      </c>
+      <c r="F99" s="1">
+        <v>3</v>
+      </c>
+      <c r="G99" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" t="s">
+        <v>79</v>
+      </c>
+      <c r="D100" t="s">
+        <v>90</v>
+      </c>
+      <c r="E100" t="s">
+        <v>104</v>
+      </c>
+      <c r="F100" s="1">
+        <v>3</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" t="s">
+        <v>80</v>
+      </c>
+      <c r="D101" t="s">
+        <v>89</v>
+      </c>
+      <c r="E101" t="s">
+        <v>104</v>
+      </c>
+      <c r="F101" s="1">
+        <v>3</v>
+      </c>
+      <c r="G101" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" t="s">
+        <v>81</v>
+      </c>
+      <c r="D102" t="s">
+        <v>87</v>
+      </c>
+      <c r="E102" t="s">
+        <v>103</v>
+      </c>
+      <c r="F102" s="1">
+        <v>3</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" t="s">
+        <v>81</v>
+      </c>
+      <c r="D103" t="s">
+        <v>87</v>
+      </c>
+      <c r="E103" t="s">
+        <v>104</v>
+      </c>
+      <c r="F103" s="1">
+        <v>3</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" t="s">
+        <v>81</v>
+      </c>
+      <c r="D104" t="s">
+        <v>100</v>
+      </c>
+      <c r="E104" t="s">
+        <v>104</v>
+      </c>
+      <c r="F104" s="1">
+        <v>3</v>
+      </c>
+      <c r="G104" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105" t="s">
         <v>82</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D105" t="s">
         <v>90</v>
       </c>
-      <c r="E95" t="s">
-        <v>103</v>
-      </c>
-      <c r="F95" s="1">
-        <v>3</v>
-      </c>
-      <c r="G95" s="1">
+      <c r="E105" t="s">
+        <v>104</v>
+      </c>
+      <c r="F105" s="1">
+        <v>3</v>
+      </c>
+      <c r="G105" s="1">
         <v>2</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -1730,7 +1730,7 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
@@ -1753,7 +1753,7 @@
         <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F60" s="1">
         <v>3</v>
@@ -2719,7 +2719,7 @@
         <v>87</v>
       </c>
       <c r="E102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F102" s="1">
         <v>3</v>
@@ -2742,7 +2742,7 @@
         <v>87</v>
       </c>
       <c r="E103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F103" s="1">
         <v>3</v>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -2719,7 +2719,7 @@
         <v>87</v>
       </c>
       <c r="E102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F102" s="1">
         <v>3</v>
@@ -2742,7 +2742,7 @@
         <v>87</v>
       </c>
       <c r="E103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F103" s="1">
         <v>3</v>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -1730,7 +1730,7 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
@@ -1753,7 +1753,7 @@
         <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F60" s="1">
         <v>3</v>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="527" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="507" uniqueCount="106">
   <si>
     <t>pull_item</t>
   </si>
@@ -21,15 +21,15 @@
     <t>liquor (e.g, whisky, coconut wine)</t>
   </si>
   <si>
+    <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+  </si>
+  <si>
+    <t>camote</t>
+  </si>
+  <si>
     <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
   </si>
   <si>
-    <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
-  </si>
-  <si>
-    <t>camote</t>
-  </si>
-  <si>
     <t>chicken</t>
   </si>
   <si>
@@ -273,15 +273,15 @@
     <t>lipid/lapad</t>
   </si>
   <si>
+    <t>small cup</t>
+  </si>
+  <si>
+    <t>binilog</t>
+  </si>
+  <si>
     <t>putos</t>
   </si>
   <si>
-    <t>small cup</t>
-  </si>
-  <si>
-    <t>binilog</t>
-  </si>
-  <si>
     <t>bilog</t>
   </si>
   <si>
@@ -292,9 +292,6 @@
   </si>
   <si>
     <t>medium packs</t>
-  </si>
-  <si>
-    <t>papaya, mango, banana</t>
   </si>
   <si>
     <t>refilled</t>
@@ -379,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -396,13 +393,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" t="s">
         <v>105</v>
-      </c>
-      <c r="G1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2">
@@ -419,7 +416,7 @@
         <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -442,7 +439,7 @@
         <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -465,7 +462,7 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -482,13 +479,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -505,13 +502,13 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -522,19 +519,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -551,13 +548,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
         <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -568,7 +565,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -577,7 +574,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>103</v>
@@ -591,19 +588,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -614,30 +611,30 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>103</v>
       </c>
       <c r="F11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -646,33 +643,33 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -689,13 +686,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -706,16 +703,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>103</v>
@@ -729,19 +726,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -752,19 +749,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -775,16 +772,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
         <v>103</v>
@@ -798,7 +795,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -807,44 +804,44 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -853,7 +850,7 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s">
         <v>103</v>
@@ -867,19 +864,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -890,16 +887,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>103</v>
@@ -913,19 +910,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -936,7 +933,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -945,33 +942,33 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F26" s="1">
         <v>2</v>
@@ -982,16 +979,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
         <v>103</v>
@@ -1005,48 +1002,48 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
         <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F29" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1057,13 +1054,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1080,13 +1077,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
         <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
@@ -1097,39 +1094,39 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F32" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s">
         <v>103</v>
@@ -1143,25 +1140,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1172,36 +1169,36 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
         <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F35" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -1212,39 +1209,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E37" t="s">
         <v>103</v>
       </c>
       <c r="F37" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
         <v>103</v>
@@ -1258,7 +1255,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -1267,10 +1264,10 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1281,7 +1278,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
         <v>18</v>
@@ -1290,10 +1287,10 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F40" s="1">
         <v>3</v>
@@ -1304,7 +1301,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>18</v>
@@ -1313,10 +1310,10 @@
         <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" s="1">
         <v>3</v>
@@ -1327,65 +1324,65 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F42" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F43" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -1396,19 +1393,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F45" s="1">
         <v>2</v>
@@ -1419,25 +1416,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1454,7 +1451,7 @@
         <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -1465,25 +1462,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
         <v>97</v>
       </c>
       <c r="E48" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1494,36 +1491,36 @@
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
         <v>85</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F49" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
         <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F50" s="1">
         <v>3</v>
@@ -1534,45 +1531,45 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B51" t="s">
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E51" t="s">
         <v>103</v>
       </c>
       <c r="F51" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E52" t="s">
         <v>103</v>
       </c>
       <c r="F52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -1586,13 +1583,13 @@
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D53" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F53" s="1">
         <v>3</v>
@@ -1603,19 +1600,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E54" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F54" s="1">
         <v>2</v>
@@ -1626,22 +1623,22 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F55" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -1655,13 +1652,13 @@
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D56" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E56" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F56" s="1">
         <v>3</v>
@@ -1672,111 +1669,111 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E57" t="s">
         <v>103</v>
       </c>
       <c r="F57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E58" t="s">
         <v>103</v>
       </c>
       <c r="F58" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F59" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F60" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D61" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F61" s="1">
         <v>3</v>
@@ -1787,19 +1784,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
@@ -1816,13 +1813,13 @@
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
         <v>85</v>
       </c>
       <c r="E63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -1833,22 +1830,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F64" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -1856,108 +1853,108 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F65" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D66" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F66" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B67" t="s">
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E67" t="s">
         <v>103</v>
       </c>
       <c r="F67" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E68" t="s">
         <v>103</v>
       </c>
       <c r="F68" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B69" t="s">
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E69" t="s">
         <v>103</v>
@@ -1971,42 +1968,42 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B71" t="s">
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D71" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F71" s="1">
         <v>3</v>
@@ -2017,19 +2014,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F72" s="1">
         <v>3</v>
@@ -2040,25 +2037,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E73" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F73" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2069,13 +2066,13 @@
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D74" t="s">
         <v>85</v>
       </c>
       <c r="E74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -2092,42 +2089,42 @@
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D75" t="s">
         <v>84</v>
       </c>
       <c r="E75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F75" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E76" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F76" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2138,13 +2135,13 @@
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
@@ -2155,39 +2152,39 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B78" t="s">
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E78" t="s">
         <v>103</v>
       </c>
       <c r="F78" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E79" t="s">
         <v>103</v>
@@ -2201,22 +2198,22 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E80" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F80" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -2230,13 +2227,13 @@
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D81" t="s">
         <v>85</v>
       </c>
       <c r="E81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -2247,91 +2244,91 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E82" t="s">
         <v>103</v>
       </c>
       <c r="F82" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D83" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E83" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F83" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D84" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E84" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F84" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E85" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -2339,16 +2336,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D86" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E86" t="s">
         <v>103</v>
@@ -2362,19 +2359,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E87" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F87" s="1">
         <v>3</v>
@@ -2391,33 +2388,33 @@
         <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F88" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B89" t="s">
         <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E89" t="s">
         <v>103</v>
@@ -2437,13 +2434,13 @@
         <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D90" t="s">
         <v>85</v>
       </c>
       <c r="E90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F90" s="1">
         <v>2</v>
@@ -2454,19 +2451,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
         <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D91" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F91" s="1">
         <v>3</v>
@@ -2477,71 +2474,71 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
         <v>18</v>
       </c>
       <c r="C92" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F92" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B93" t="s">
         <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D93" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F93" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G93" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E94" t="s">
         <v>103</v>
       </c>
       <c r="F94" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -2549,16 +2546,16 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E95" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95" s="1">
         <v>3</v>
@@ -2569,65 +2566,65 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C96" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E96" t="s">
         <v>103</v>
       </c>
       <c r="F96" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C97" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D97" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F97" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G97" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B98" t="s">
         <v>19</v>
       </c>
       <c r="C98" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D98" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E98" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F98" s="1">
         <v>3</v>
@@ -2638,19 +2635,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B99" t="s">
         <v>19</v>
       </c>
       <c r="C99" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F99" s="1">
         <v>3</v>
@@ -2661,19 +2658,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B100" t="s">
         <v>19</v>
       </c>
       <c r="C100" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F100" s="1">
         <v>3</v>
@@ -2684,116 +2681,24 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B101" t="s">
         <v>19</v>
       </c>
       <c r="C101" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D101" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F101" s="1">
         <v>3</v>
       </c>
       <c r="G101" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" t="s">
-        <v>19</v>
-      </c>
-      <c r="C102" t="s">
-        <v>81</v>
-      </c>
-      <c r="D102" t="s">
-        <v>87</v>
-      </c>
-      <c r="E102" t="s">
-        <v>103</v>
-      </c>
-      <c r="F102" s="1">
-        <v>3</v>
-      </c>
-      <c r="G102" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" t="s">
-        <v>81</v>
-      </c>
-      <c r="D103" t="s">
-        <v>87</v>
-      </c>
-      <c r="E103" t="s">
-        <v>104</v>
-      </c>
-      <c r="F103" s="1">
-        <v>3</v>
-      </c>
-      <c r="G103" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>7</v>
-      </c>
-      <c r="B104" t="s">
-        <v>19</v>
-      </c>
-      <c r="C104" t="s">
-        <v>81</v>
-      </c>
-      <c r="D104" t="s">
-        <v>100</v>
-      </c>
-      <c r="E104" t="s">
-        <v>104</v>
-      </c>
-      <c r="F104" s="1">
-        <v>3</v>
-      </c>
-      <c r="G104" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" t="s">
-        <v>19</v>
-      </c>
-      <c r="C105" t="s">
-        <v>82</v>
-      </c>
-      <c r="D105" t="s">
-        <v>90</v>
-      </c>
-      <c r="E105" t="s">
-        <v>104</v>
-      </c>
-      <c r="F105" s="1">
-        <v>3</v>
-      </c>
-      <c r="G105" s="1">
         <v>2</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="507" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="492" uniqueCount="105">
   <si>
     <t>pull_item</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>BAROTAC NUEVO</t>
-  </si>
-  <si>
-    <t>BAROTAC VIEJO</t>
   </si>
   <si>
     <t>BATAD</t>
@@ -376,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -390,16 +387,16 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
         <v>104</v>
-      </c>
-      <c r="G1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2">
@@ -413,10 +410,10 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -436,10 +433,10 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -459,10 +456,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -482,10 +479,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -505,10 +502,10 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -528,10 +525,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -551,10 +548,10 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -574,10 +571,10 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F9" s="1">
         <v>3</v>
@@ -597,10 +594,10 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -620,10 +617,10 @@
         <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -643,10 +640,10 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
@@ -666,10 +663,10 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -689,10 +686,10 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -712,10 +709,10 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
@@ -735,10 +732,10 @@
         <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -758,10 +755,10 @@
         <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -781,10 +778,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F18" s="1">
         <v>3</v>
@@ -804,10 +801,10 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -827,10 +824,10 @@
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
@@ -850,10 +847,10 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -873,10 +870,10 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -896,10 +893,10 @@
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
@@ -919,10 +916,10 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -942,10 +939,10 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -965,10 +962,10 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F26" s="1">
         <v>2</v>
@@ -988,10 +985,10 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="1">
         <v>2</v>
@@ -1011,10 +1008,10 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
@@ -1034,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
@@ -1057,10 +1054,10 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1080,10 +1077,10 @@
         <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
@@ -1103,10 +1100,10 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -1126,10 +1123,10 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F33" s="1">
         <v>3</v>
@@ -1149,10 +1146,10 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F34" s="1">
         <v>2</v>
@@ -1172,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" s="1">
         <v>3</v>
@@ -1195,10 +1192,10 @@
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -1218,10 +1215,10 @@
         <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F37" s="1">
         <v>3</v>
@@ -1241,10 +1238,10 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F38" s="1">
         <v>3</v>
@@ -1264,10 +1261,10 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1287,10 +1284,10 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" s="1">
         <v>3</v>
@@ -1310,10 +1307,10 @@
         <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="1">
         <v>3</v>
@@ -1333,10 +1330,10 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F42" s="1">
         <v>2</v>
@@ -1356,10 +1353,10 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F43" s="1">
         <v>2</v>
@@ -1379,10 +1376,10 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -1402,10 +1399,10 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F45" s="1">
         <v>2</v>
@@ -1425,10 +1422,10 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F46" s="1">
         <v>3</v>
@@ -1439,19 +1436,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -1462,7 +1459,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
@@ -1471,62 +1468,62 @@
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F48" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E49" t="s">
         <v>102</v>
       </c>
       <c r="F49" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D50" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F50" s="1">
         <v>3</v>
       </c>
       <c r="G50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1537,39 +1534,39 @@
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E52" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F52" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -1577,53 +1574,53 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E53" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F53" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F54" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
@@ -1632,30 +1629,30 @@
         <v>56</v>
       </c>
       <c r="D55" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E55" t="s">
         <v>102</v>
       </c>
       <c r="F55" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D56" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E56" t="s">
         <v>102</v>
@@ -1678,21 +1675,21 @@
         <v>57</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E57" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
@@ -1701,21 +1698,21 @@
         <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F58" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
@@ -1724,33 +1721,33 @@
         <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E59" t="s">
         <v>102</v>
       </c>
       <c r="F59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F60" s="1">
         <v>2</v>
@@ -1761,30 +1758,30 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E61" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F61" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
@@ -1793,10 +1790,10 @@
         <v>60</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
@@ -1816,21 +1813,21 @@
         <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F63" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
@@ -1839,21 +1836,21 @@
         <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E64" t="s">
         <v>102</v>
       </c>
       <c r="F64" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
@@ -1862,7 +1859,7 @@
         <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E65" t="s">
         <v>102</v>
@@ -1876,7 +1873,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
@@ -1885,10 +1882,10 @@
         <v>62</v>
       </c>
       <c r="D66" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F66" s="1">
         <v>3</v>
@@ -1899,19 +1896,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67" t="s">
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D67" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F67" s="1">
         <v>3</v>
@@ -1922,7 +1919,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>18</v>
@@ -1931,21 +1928,21 @@
         <v>63</v>
       </c>
       <c r="D68" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F68" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B69" t="s">
         <v>18</v>
@@ -1954,10 +1951,10 @@
         <v>63</v>
       </c>
       <c r="D69" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E69" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F69" s="1">
         <v>3</v>
@@ -1968,25 +1965,25 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D70" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E70" t="s">
         <v>102</v>
       </c>
       <c r="F70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2000,39 +1997,39 @@
         <v>64</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F71" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D72" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E72" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F72" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2046,10 +2043,10 @@
         <v>65</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F73" s="1">
         <v>2</v>
@@ -2069,10 +2066,10 @@
         <v>66</v>
       </c>
       <c r="D74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E74" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -2089,13 +2086,13 @@
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D75" t="s">
         <v>84</v>
       </c>
       <c r="E75" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F75" s="1">
         <v>2</v>
@@ -2106,7 +2103,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
@@ -2115,21 +2112,21 @@
         <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E76" t="s">
         <v>102</v>
       </c>
       <c r="F76" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
@@ -2138,7 +2135,7 @@
         <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E77" t="s">
         <v>102</v>
@@ -2161,21 +2158,21 @@
         <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F78" s="1">
         <v>3</v>
       </c>
       <c r="G78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
@@ -2184,10 +2181,10 @@
         <v>69</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E79" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F79" s="1">
         <v>2</v>
@@ -2198,7 +2195,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
@@ -2207,16 +2204,16 @@
         <v>69</v>
       </c>
       <c r="D80" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F80" s="1">
         <v>3</v>
       </c>
       <c r="G80" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2230,10 +2227,10 @@
         <v>70</v>
       </c>
       <c r="D81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -2244,19 +2241,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D82" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E82" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F82" s="1">
         <v>3</v>
@@ -2279,7 +2276,7 @@
         <v>84</v>
       </c>
       <c r="E83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F83" s="1">
         <v>2</v>
@@ -2290,30 +2287,30 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E84" t="s">
         <v>102</v>
       </c>
       <c r="F84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G84" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
@@ -2322,67 +2319,67 @@
         <v>72</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E85" t="s">
         <v>102</v>
       </c>
       <c r="F85" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F86" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E87" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G87" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
         <v>18</v>
@@ -2391,7 +2388,7 @@
         <v>74</v>
       </c>
       <c r="D88" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
         <v>102</v>
@@ -2405,7 +2402,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
         <v>18</v>
@@ -2414,30 +2411,30 @@
         <v>75</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E89" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F89" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G89" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B90" t="s">
         <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D90" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E90" t="s">
         <v>102</v>
@@ -2451,19 +2448,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D91" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F91" s="1">
         <v>3</v>
@@ -2474,48 +2471,48 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D92" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E92" t="s">
         <v>102</v>
       </c>
       <c r="F92" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F93" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2526,13 +2523,13 @@
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D94" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
@@ -2543,19 +2540,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
         <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D95" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E95" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F95" s="1">
         <v>3</v>
@@ -2566,19 +2563,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
         <v>19</v>
       </c>
       <c r="C96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D96" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F96" s="1">
         <v>3</v>
@@ -2589,19 +2586,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B97" t="s">
         <v>19</v>
       </c>
       <c r="C97" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D97" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F97" s="1">
         <v>3</v>
@@ -2621,7 +2618,7 @@
         <v>81</v>
       </c>
       <c r="D98" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E98" t="s">
         <v>102</v>
@@ -2630,75 +2627,6 @@
         <v>3</v>
       </c>
       <c r="G98" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>2</v>
-      </c>
-      <c r="B99" t="s">
-        <v>19</v>
-      </c>
-      <c r="C99" t="s">
-        <v>81</v>
-      </c>
-      <c r="D99" t="s">
-        <v>86</v>
-      </c>
-      <c r="E99" t="s">
-        <v>103</v>
-      </c>
-      <c r="F99" s="1">
-        <v>3</v>
-      </c>
-      <c r="G99" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>7</v>
-      </c>
-      <c r="B100" t="s">
-        <v>19</v>
-      </c>
-      <c r="C100" t="s">
-        <v>81</v>
-      </c>
-      <c r="D100" t="s">
-        <v>99</v>
-      </c>
-      <c r="E100" t="s">
-        <v>103</v>
-      </c>
-      <c r="F100" s="1">
-        <v>3</v>
-      </c>
-      <c r="G100" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>2</v>
-      </c>
-      <c r="B101" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" t="s">
-        <v>82</v>
-      </c>
-      <c r="D101" t="s">
-        <v>90</v>
-      </c>
-      <c r="E101" t="s">
-        <v>103</v>
-      </c>
-      <c r="F101" s="1">
-        <v>3</v>
-      </c>
-      <c r="G101" s="1">
         <v>2</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
+++ b/outputs/master_rename_build/tables/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="492" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="492" uniqueCount="106">
   <si>
     <t>pull_item</t>
   </si>
@@ -162,6 +162,9 @@
     <t>ALIMODIAN</t>
   </si>
   <si>
+    <t>ANILAO</t>
+  </si>
+  <si>
     <t>BALASAN</t>
   </si>
   <si>
@@ -300,10 +303,10 @@
     <t>tumpok</t>
   </si>
   <si>
+    <t>pieces</t>
+  </si>
+  <si>
     <t>pack</t>
-  </si>
-  <si>
-    <t>pieces</t>
   </si>
   <si>
     <t>cone</t>
@@ -387,16 +390,16 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
@@ -410,10 +413,10 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -433,10 +436,10 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -456,10 +459,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -479,10 +482,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -502,10 +505,10 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -525,10 +528,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -548,10 +551,10 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -571,10 +574,10 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F9" s="1">
         <v>3</v>
@@ -594,10 +597,10 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -617,10 +620,10 @@
         <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -640,10 +643,10 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
@@ -663,10 +666,10 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -686,10 +689,10 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -709,10 +712,10 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
@@ -732,10 +735,10 @@
         <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -755,10 +758,10 @@
         <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -778,10 +781,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F18" s="1">
         <v>3</v>
@@ -801,10 +804,10 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -824,10 +827,10 @@
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
@@ -847,10 +850,10 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -870,10 +873,10 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -893,10 +896,10 @@
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
@@ -916,10 +919,10 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -939,10 +942,10 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -962,10 +965,10 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="1">
         <v>2</v>
@@ -985,10 +988,10 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="1">
         <v>2</v>
@@ -1008,10 +1011,10 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
@@ -1031,10 +1034,10 @@
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
@@ -1054,10 +1057,10 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1077,10 +1080,10 @@
         <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
@@ -1100,10 +1103,10 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -1123,10 +1126,10 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F33" s="1">
         <v>3</v>
@@ -1146,10 +1149,10 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F34" s="1">
         <v>2</v>
@@ -1169,10 +1172,10 @@
         <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="1">
         <v>3</v>
@@ -1192,10 +1195,10 @@
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -1215,10 +1218,10 @@
         <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F37" s="1">
         <v>3</v>
@@ -1238,10 +1241,10 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F38" s="1">
         <v>3</v>
@@ -1261,10 +1264,10 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1284,10 +1287,10 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F40" s="1">
         <v>3</v>
@@ -1307,10 +1310,10 @@
         <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F41" s="1">
         <v>3</v>
@@ -1330,10 +1333,10 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F42" s="1">
         <v>2</v>
@@ -1353,10 +1356,10 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F43" s="1">
         <v>2</v>
@@ -1367,7 +1370,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
@@ -1376,7 +1379,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E44" t="s">
         <v>102</v>
@@ -1390,25 +1393,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F45" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1419,13 +1422,13 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F46" s="1">
         <v>3</v>
@@ -1442,13 +1445,13 @@
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
         <v>96</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -1465,13 +1468,13 @@
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" s="1">
         <v>2</v>
@@ -1488,13 +1491,13 @@
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F49" s="1">
         <v>3</v>
@@ -1511,13 +1514,13 @@
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F50" s="1">
         <v>3</v>
@@ -1534,13 +1537,13 @@
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F51" s="1">
         <v>3</v>
@@ -1557,13 +1560,13 @@
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F52" s="1">
         <v>2</v>
@@ -1580,13 +1583,13 @@
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F53" s="1">
         <v>2</v>
@@ -1603,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F54" s="1">
         <v>3</v>
@@ -1626,13 +1629,13 @@
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E55" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F55" s="1">
         <v>3</v>
@@ -1649,13 +1652,13 @@
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F56" s="1">
         <v>3</v>
@@ -1672,13 +1675,13 @@
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F57" s="1">
         <v>2</v>
@@ -1695,13 +1698,13 @@
         <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F58" s="1">
         <v>2</v>
@@ -1718,13 +1721,13 @@
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
@@ -1741,13 +1744,13 @@
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D60" t="s">
         <v>96</v>
       </c>
       <c r="E60" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F60" s="1">
         <v>2</v>
@@ -1764,13 +1767,13 @@
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E61" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F61" s="1">
         <v>2</v>
@@ -1787,13 +1790,13 @@
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E62" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
@@ -1810,13 +1813,13 @@
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E63" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
@@ -1833,13 +1836,13 @@
         <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E64" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
@@ -1856,13 +1859,13 @@
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E65" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F65" s="1">
         <v>3</v>
@@ -1879,13 +1882,13 @@
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E66" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F66" s="1">
         <v>3</v>
@@ -1902,13 +1905,13 @@
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D67" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F67" s="1">
         <v>3</v>
@@ -1925,13 +1928,13 @@
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E68" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F68" s="1">
         <v>2</v>
@@ -1948,13 +1951,13 @@
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E69" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F69" s="1">
         <v>3</v>
@@ -1971,13 +1974,13 @@
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F70" s="1">
         <v>3</v>
@@ -1994,13 +1997,13 @@
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F71" s="1">
         <v>2</v>
@@ -2017,13 +2020,13 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E72" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F72" s="1">
         <v>2</v>
@@ -2040,13 +2043,13 @@
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E73" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F73" s="1">
         <v>2</v>
@@ -2063,13 +2066,13 @@
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -2086,13 +2089,13 @@
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E75" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F75" s="1">
         <v>2</v>
@@ -2109,13 +2112,13 @@
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D76" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E76" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F76" s="1">
         <v>3</v>
@@ -2132,13 +2135,13 @@
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E77" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
@@ -2155,13 +2158,13 @@
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D78" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E78" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F78" s="1">
         <v>3</v>
@@ -2178,13 +2181,13 @@
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E79" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F79" s="1">
         <v>2</v>
@@ -2201,13 +2204,13 @@
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F80" s="1">
         <v>3</v>
@@ -2224,13 +2227,13 @@
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -2247,13 +2250,13 @@
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D82" t="s">
         <v>96</v>
       </c>
       <c r="E82" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F82" s="1">
         <v>3</v>
@@ -2270,13 +2273,13 @@
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F83" s="1">
         <v>2</v>
@@ -2293,13 +2296,13 @@
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F84" s="1">
         <v>2</v>
@@ -2316,13 +2319,13 @@
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D85" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F85" s="1">
         <v>3</v>
@@ -2339,13 +2342,13 @@
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F86" s="1">
         <v>3</v>
@@ -2362,13 +2365,13 @@
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E87" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F87" s="1">
         <v>2</v>
@@ -2385,13 +2388,13 @@
         <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D88" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E88" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F88" s="1">
         <v>3</v>
@@ -2408,13 +2411,13 @@
         <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D89" t="s">
         <v>96</v>
       </c>
       <c r="E89" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F89" s="1">
         <v>2</v>
@@ -2431,13 +2434,13 @@
         <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D90" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E90" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F90" s="1">
         <v>2</v>
@@ -2454,13 +2457,13 @@
         <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E91" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F91" s="1">
         <v>3</v>
@@ -2477,13 +2480,13 @@
         <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E92" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F92" s="1">
         <v>3</v>
@@ -2500,13 +2503,13 @@
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D93" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E93" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F93" s="1">
         <v>3</v>
@@ -2523,13 +2526,13 @@
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
@@ -2546,13 +2549,13 @@
         <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E95" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F95" s="1">
         <v>3</v>
@@ -2569,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="C96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E96" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F96" s="1">
         <v>3</v>
@@ -2592,13 +2595,13 @@
         <v>19</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D97" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E97" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F97" s="1">
         <v>3</v>
@@ -2615,13 +2618,13 @@
         <v>19</v>
       </c>
       <c r="C98" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D98" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E98" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F98" s="1">
         <v>3</v>
